--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168605</v>
+        <v>122168622</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -708,16 +708,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499168</v>
+        <v>499152</v>
       </c>
       <c r="R2" t="n">
-        <v>6816707</v>
+        <v>6816787</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168590</v>
+        <v>122168639</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -822,16 +814,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -840,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499211</v>
+        <v>499173</v>
       </c>
       <c r="R3" t="n">
-        <v>6816807</v>
+        <v>6816744</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168500</v>
+        <v>122168594</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>78645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,45 +903,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499173</v>
+        <v>499210</v>
       </c>
       <c r="R4" t="n">
-        <v>6816743</v>
+        <v>6816765</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168639</v>
+        <v>122168605</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1050,8 +1034,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499173</v>
+        <v>499168</v>
       </c>
       <c r="R5" t="n">
-        <v>6816744</v>
+        <v>6816707</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>90779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1131,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R6" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168594</v>
+        <v>122168634</v>
       </c>
       <c r="B7" t="n">
         <v>78645</v>
@@ -1262,28 +1262,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499210</v>
+        <v>499150</v>
       </c>
       <c r="R7" t="n">
-        <v>6816765</v>
+        <v>6816722</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1457,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168622</v>
+        <v>122168590</v>
       </c>
       <c r="B9" t="n">
         <v>78645</v>
@@ -1490,8 +1482,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499152</v>
+        <v>499211</v>
       </c>
       <c r="R9" t="n">
-        <v>6816787</v>
+        <v>6816807</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168622</v>
+        <v>122168651</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,8 +708,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499152</v>
+        <v>499167</v>
       </c>
       <c r="R2" t="n">
-        <v>6816787</v>
+        <v>6816739</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168639</v>
+        <v>122168622</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499173</v>
+        <v>499152</v>
       </c>
       <c r="R3" t="n">
-        <v>6816744</v>
+        <v>6816787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168594</v>
+        <v>122168634</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,28 +928,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499210</v>
+        <v>499150</v>
       </c>
       <c r="R4" t="n">
-        <v>6816765</v>
+        <v>6816722</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,7 +1004,7 @@
         <v>122168605</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168500</v>
+        <v>122168594</v>
       </c>
       <c r="B6" t="n">
-        <v>90779</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,45 +1131,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499173</v>
+        <v>499210</v>
       </c>
       <c r="R6" t="n">
-        <v>6816743</v>
+        <v>6816765</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>90789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1272,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R7" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168651</v>
+        <v>122168590</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,7 +1378,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1386,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499167</v>
+        <v>499211</v>
       </c>
       <c r="R8" t="n">
-        <v>6816739</v>
+        <v>6816807</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168590</v>
+        <v>122168639</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,16 +1490,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499211</v>
+        <v>499173</v>
       </c>
       <c r="R9" t="n">
-        <v>6816807</v>
+        <v>6816744</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168651</v>
+        <v>122168590</v>
       </c>
       <c r="B2" t="n">
         <v>78646</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499167</v>
+        <v>499211</v>
       </c>
       <c r="R2" t="n">
-        <v>6816739</v>
+        <v>6816807</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168622</v>
+        <v>122168651</v>
       </c>
       <c r="B3" t="n">
         <v>78646</v>
@@ -822,8 +822,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499152</v>
+        <v>499167</v>
       </c>
       <c r="R3" t="n">
-        <v>6816787</v>
+        <v>6816739</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168634</v>
+        <v>122168622</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -938,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499150</v>
+        <v>499152</v>
       </c>
       <c r="R4" t="n">
-        <v>6816722</v>
+        <v>6816787</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168605</v>
+        <v>122168594</v>
       </c>
       <c r="B5" t="n">
         <v>78646</v>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499168</v>
+        <v>499210</v>
       </c>
       <c r="R5" t="n">
-        <v>6816707</v>
+        <v>6816765</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168594</v>
+        <v>122168639</v>
       </c>
       <c r="B6" t="n">
         <v>78646</v>
@@ -1148,28 +1156,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499210</v>
+        <v>499173</v>
       </c>
       <c r="R6" t="n">
-        <v>6816765</v>
+        <v>6816744</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168500</v>
+        <v>122168634</v>
       </c>
       <c r="B7" t="n">
-        <v>90789</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,33 +1245,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499173</v>
+        <v>499150</v>
       </c>
       <c r="R7" t="n">
-        <v>6816743</v>
+        <v>6816722</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168590</v>
+        <v>122168500</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>90789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,31 +1351,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1394,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499211</v>
+        <v>499173</v>
       </c>
       <c r="R8" t="n">
-        <v>6816807</v>
+        <v>6816743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168639</v>
+        <v>122168605</v>
       </c>
       <c r="B9" t="n">
         <v>78646</v>
@@ -1490,8 +1482,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499173</v>
+        <v>499168</v>
       </c>
       <c r="R9" t="n">
-        <v>6816744</v>
+        <v>6816707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168500</v>
+        <v>122168605</v>
       </c>
       <c r="B8" t="n">
-        <v>90789</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499173</v>
+        <v>499168</v>
       </c>
       <c r="R8" t="n">
-        <v>6816743</v>
+        <v>6816707</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168605</v>
+        <v>122168500</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>90789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499168</v>
+        <v>499173</v>
       </c>
       <c r="R9" t="n">
-        <v>6816707</v>
+        <v>6816743</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122168590</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168651</v>
+        <v>122168594</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499167</v>
+        <v>499210</v>
       </c>
       <c r="R3" t="n">
-        <v>6816739</v>
+        <v>6816765</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168622</v>
+        <v>122168605</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,8 +936,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -946,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499152</v>
+        <v>499168</v>
       </c>
       <c r="R4" t="n">
-        <v>6816787</v>
+        <v>6816707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168594</v>
+        <v>122168634</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,28 +1050,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499210</v>
+        <v>499150</v>
       </c>
       <c r="R5" t="n">
-        <v>6816765</v>
+        <v>6816722</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168639</v>
+        <v>122168622</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499173</v>
+        <v>499152</v>
       </c>
       <c r="R6" t="n">
-        <v>6816744</v>
+        <v>6816787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>90801</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1272,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R7" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168605</v>
+        <v>122168639</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,16 +1376,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499168</v>
+        <v>499173</v>
       </c>
       <c r="R8" t="n">
-        <v>6816707</v>
+        <v>6816744</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168500</v>
+        <v>122168651</v>
       </c>
       <c r="B9" t="n">
-        <v>90789</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499173</v>
+        <v>499167</v>
       </c>
       <c r="R9" t="n">
-        <v>6816743</v>
+        <v>6816739</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168590</v>
+        <v>122168594</v>
       </c>
       <c r="B2" t="n">
         <v>78651</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499211</v>
+        <v>499210</v>
       </c>
       <c r="R2" t="n">
-        <v>6816807</v>
+        <v>6816765</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168594</v>
+        <v>122168651</v>
       </c>
       <c r="B3" t="n">
         <v>78651</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499210</v>
+        <v>499167</v>
       </c>
       <c r="R3" t="n">
-        <v>6816765</v>
+        <v>6816739</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168605</v>
+        <v>122168590</v>
       </c>
       <c r="B4" t="n">
         <v>78651</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499168</v>
+        <v>499211</v>
       </c>
       <c r="R4" t="n">
-        <v>6816707</v>
+        <v>6816807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>90808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R5" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168622</v>
+        <v>122168605</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1156,8 +1164,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1166,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499152</v>
+        <v>499168</v>
       </c>
       <c r="R6" t="n">
-        <v>6816787</v>
+        <v>6816707</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168500</v>
+        <v>122168639</v>
       </c>
       <c r="B7" t="n">
-        <v>90801</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,33 +1261,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1283,7 +1291,7 @@
         <v>499173</v>
       </c>
       <c r="R7" t="n">
-        <v>6816743</v>
+        <v>6816744</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168639</v>
+        <v>122168634</v>
       </c>
       <c r="B8" t="n">
         <v>78651</v>
@@ -1386,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499173</v>
+        <v>499150</v>
       </c>
       <c r="R8" t="n">
-        <v>6816744</v>
+        <v>6816722</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168651</v>
+        <v>122168622</v>
       </c>
       <c r="B9" t="n">
         <v>78651</v>
@@ -1482,16 +1490,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499167</v>
+        <v>499152</v>
       </c>
       <c r="R9" t="n">
-        <v>6816739</v>
+        <v>6816787</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168594</v>
+        <v>122168639</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -708,28 +703,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499210</v>
+        <v>499173</v>
       </c>
       <c r="R2" t="n">
-        <v>6816765</v>
+        <v>6816744</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168651</v>
+        <v>122168622</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,11 +794,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -822,16 +804,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -840,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499167</v>
+        <v>499152</v>
       </c>
       <c r="R3" t="n">
-        <v>6816739</v>
+        <v>6816787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -906,7 +880,7 @@
         <v>122168590</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,11 +894,6 @@
       </c>
       <c r="E4" t="n">
         <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1017,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168500</v>
+        <v>122168651</v>
       </c>
       <c r="B5" t="n">
-        <v>90808</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1002,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,7 +1021,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499173</v>
+        <v>499167</v>
       </c>
       <c r="R5" t="n">
-        <v>6816743</v>
+        <v>6816739</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168605</v>
+        <v>122168634</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,11 +1113,6 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1164,16 +1123,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499168</v>
+        <v>499150</v>
       </c>
       <c r="R6" t="n">
-        <v>6816707</v>
+        <v>6816722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168639</v>
+        <v>122168594</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,11 +1214,6 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1278,20 +1224,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499173</v>
+        <v>499210</v>
       </c>
       <c r="R7" t="n">
-        <v>6816744</v>
+        <v>6816765</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>90813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1321,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1394,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R8" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168622</v>
+        <v>122168605</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,11 +1432,6 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1490,8 +1442,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1500,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499152</v>
+        <v>499168</v>
       </c>
       <c r="R9" t="n">
-        <v>6816787</v>
+        <v>6816707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168634</v>
+        <v>122168500</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>90813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,20 +1111,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499150</v>
+        <v>499173</v>
       </c>
       <c r="R6" t="n">
-        <v>6816722</v>
+        <v>6816743</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168594</v>
+        <v>122168634</v>
       </c>
       <c r="B7" t="n">
         <v>78652</v>
@@ -1224,28 +1232,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499210</v>
+        <v>499150</v>
       </c>
       <c r="R7" t="n">
-        <v>6816765</v>
+        <v>6816722</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168500</v>
+        <v>122168594</v>
       </c>
       <c r="B8" t="n">
-        <v>90813</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499173</v>
+        <v>499210</v>
       </c>
       <c r="R8" t="n">
-        <v>6816743</v>
+        <v>6816765</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168500</v>
+        <v>122168634</v>
       </c>
       <c r="B6" t="n">
-        <v>90813</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,28 +1111,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1141,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499173</v>
+        <v>499150</v>
       </c>
       <c r="R6" t="n">
-        <v>6816743</v>
+        <v>6816722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1196,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168634</v>
+        <v>122168594</v>
       </c>
       <c r="B7" t="n">
         <v>78652</v>
@@ -1232,20 +1224,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499150</v>
+        <v>499210</v>
       </c>
       <c r="R7" t="n">
-        <v>6816722</v>
+        <v>6816765</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168594</v>
+        <v>122168500</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>90813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499210</v>
+        <v>499173</v>
       </c>
       <c r="R8" t="n">
-        <v>6816765</v>
+        <v>6816743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168639</v>
+        <v>122168622</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499173</v>
+        <v>499152</v>
       </c>
       <c r="R2" t="n">
-        <v>6816744</v>
+        <v>6816787</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168622</v>
+        <v>122168634</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,6 +798,11 @@
       </c>
       <c r="E3" t="n">
         <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -814,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499152</v>
+        <v>499150</v>
       </c>
       <c r="R3" t="n">
-        <v>6816787</v>
+        <v>6816722</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168590</v>
+        <v>122168500</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,26 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -923,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499211</v>
+        <v>499173</v>
       </c>
       <c r="R4" t="n">
-        <v>6816807</v>
+        <v>6816743</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168651</v>
+        <v>122168590</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1004,6 +1019,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1016,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1032,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499167</v>
+        <v>499211</v>
       </c>
       <c r="R5" t="n">
-        <v>6816739</v>
+        <v>6816807</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168634</v>
+        <v>122168605</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,6 +1133,11 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1123,8 +1148,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499150</v>
+        <v>499168</v>
       </c>
       <c r="R6" t="n">
-        <v>6816722</v>
+        <v>6816707</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122168594</v>
+        <v>122168651</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,6 +1247,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1226,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1238,14 +1276,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499210</v>
+        <v>499167</v>
       </c>
       <c r="R7" t="n">
-        <v>6816765</v>
+        <v>6816739</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168500</v>
+        <v>122168594</v>
       </c>
       <c r="B8" t="n">
-        <v>90813</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,40 +1359,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499173</v>
+        <v>499210</v>
       </c>
       <c r="R8" t="n">
-        <v>6816743</v>
+        <v>6816765</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168605</v>
+        <v>122168639</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,6 +1475,11 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1442,16 +1490,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1460,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499168</v>
+        <v>499173</v>
       </c>
       <c r="R9" t="n">
-        <v>6816707</v>
+        <v>6816744</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 52927-2024 artfynd.xlsx
+++ b/artfynd/A 52927-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122168622</v>
+        <v>122168594</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -708,20 +708,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>växtbostupet, Dlr</t>
+          <t>västbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499152</v>
+        <v>499210</v>
       </c>
       <c r="R2" t="n">
-        <v>6816787</v>
+        <v>6816765</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122168634</v>
+        <v>122168590</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -814,8 +822,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -824,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499150</v>
+        <v>499211</v>
       </c>
       <c r="R3" t="n">
-        <v>6816722</v>
+        <v>6816807</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122168500</v>
+        <v>122168605</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -927,7 +943,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -938,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499173</v>
+        <v>499168</v>
       </c>
       <c r="R4" t="n">
-        <v>6816743</v>
+        <v>6816707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122168590</v>
+        <v>122168500</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,31 +1033,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499211</v>
+        <v>499173</v>
       </c>
       <c r="R5" t="n">
-        <v>6816807</v>
+        <v>6816743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122168605</v>
+        <v>122168639</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1148,16 +1164,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1166,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499168</v>
+        <v>499173</v>
       </c>
       <c r="R6" t="n">
-        <v>6816707</v>
+        <v>6816744</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1343,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122168594</v>
+        <v>122168622</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1376,28 +1384,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>västbostupet, Dlr</t>
+          <t>växtbostupet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499210</v>
+        <v>499152</v>
       </c>
       <c r="R8" t="n">
-        <v>6816765</v>
+        <v>6816787</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122168639</v>
+        <v>122168634</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499173</v>
+        <v>499150</v>
       </c>
       <c r="R9" t="n">
-        <v>6816744</v>
+        <v>6816722</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
